--- a/inst/templates/DataImportConfiguration.xlsx
+++ b/inst/templates/DataImportConfiguration.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="DataFiles" sheetId="1" state="visible" r:id="rId3"/>
@@ -39,7 +39,7 @@
     <t xml:space="preserve">DataClass</t>
   </si>
   <si>
-    <t xml:space="preserve">identifier for file filtering</t>
+    <t xml:space="preserve">identifier for file filtering (character)</t>
   </si>
   <si>
     <r>
